--- a/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2016_T2_0.xlsx
+++ b/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2016_T2_0.xlsx
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>93</t>
+    <t>89</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -57,16 +57,16 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>0.043</t>
-  </si>
-  <si>
-    <t>(0.021)</t>
-  </si>
-  <si>
-    <t>0.226</t>
-  </si>
-  <si>
-    <t>(0.044)</t>
+    <t>0.045</t>
+  </si>
+  <si>
+    <t>(0.022)</t>
+  </si>
+  <si>
+    <t>0.236</t>
+  </si>
+  <si>
+    <t>(0.045)</t>
   </si>
   <si>
     <t>0.000</t>
@@ -75,10 +75,10 @@
     <t>(0.000)</t>
   </si>
   <si>
-    <t>0.398</t>
-  </si>
-  <si>
-    <t>(0.091)</t>
+    <t>0.416</t>
+  </si>
+  <si>
+    <t>(0.094)</t>
   </si>
   <si>
     <t>21</t>
@@ -108,7 +108,7 @@
     <t>(0.402)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>.n</t>
@@ -123,13 +123,13 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.005</t>
-  </si>
-  <si>
-    <t>0.536***</t>
-  </si>
-  <si>
-    <t>1.697***</t>
+    <t>0.003</t>
+  </si>
+  <si>
+    <t>0.526***</t>
+  </si>
+  <si>
+    <t>1.680***</t>
   </si>
 </sst>
 </file>
